--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:45</t>
+    <t xml:space="preserve">2026-09-09 22:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:32</t>
+    <t xml:space="preserve">2026-09-12 19:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:48</t>
+    <t xml:space="preserve">2026-09-24 00:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:26</t>
+    <t xml:space="preserve">2026-09-27 23:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -523,7 +523,7 @@
         <v>2019</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2.53</v>
+        <v>25.35</v>
       </c>
     </row>
     <row r="3">
@@ -540,7 +540,7 @@
         <v>2019</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.63</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="4">
@@ -557,7 +557,7 @@
         <v>2019</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.48</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="5">
@@ -574,7 +574,7 @@
         <v>2019</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.46</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="6">
@@ -591,7 +591,7 @@
         <v>2019</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.18</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="7">
@@ -608,7 +608,7 @@
         <v>2019</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="8">
@@ -625,7 +625,7 @@
         <v>2019</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.17</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="9">
@@ -642,7 +642,7 @@
         <v>2019</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.24</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="10">
@@ -659,7 +659,7 @@
         <v>2019</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-0.47</v>
+        <v>-4.67</v>
       </c>
     </row>
     <row r="11">
@@ -676,7 +676,7 @@
         <v>2019</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.5</v>
+        <v>-5.02</v>
       </c>
     </row>
     <row r="12">
@@ -693,7 +693,7 @@
         <v>2019</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-0.53</v>
+        <v>-5.33</v>
       </c>
     </row>
     <row r="13">
@@ -710,7 +710,7 @@
         <v>2019</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-0.62</v>
+        <v>-6.17</v>
       </c>
     </row>
     <row r="14">
@@ -727,7 +727,7 @@
         <v>2019</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-1.13</v>
+        <v>-11.26</v>
       </c>
     </row>
     <row r="15">
@@ -744,7 +744,7 @@
         <v>2019</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-1.23</v>
+        <v>-12.33</v>
       </c>
     </row>
     <row r="16">
@@ -761,7 +761,7 @@
         <v>2019</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-2.45</v>
+        <v>-24.55</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:09</t>
+    <t xml:space="preserve">2026-10-01 20:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:55</t>
+    <t xml:space="preserve">2026-10-02 13:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:25</t>
+    <t xml:space="preserve">2026-10-04 08:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:11</t>
+    <t xml:space="preserve">2026-10-05 08:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
